--- a/LumaWorks_Retail_Multi_Year_Sales_Consolidation.xlsx
+++ b/LumaWorks_Retail_Multi_Year_Sales_Consolidation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SURFACE PRO4\Desktop\Power Query Projects\LumaWorks_Retail_PowerQuery_Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2121DD71-24A6-49CD-BDCF-DF1453A2E8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F213E3-E503-4C26-8D07-57270FBF5290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{E9C4806A-9812-46A5-A573-9DC5AFFDB216}"/>
   </bookViews>
@@ -220,7 +220,7 @@
     <tableColumn id="4" xr3:uid="{166EEE1E-2929-4AAF-8AAA-B58C3B394545}" uniqueName="4" name="Unit Price" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{25E0AC86-6DDC-4A6D-B832-90AAE0C098E7}" uniqueName="5" name="Quarter" queryTableFieldId="5"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
